--- a/questionnaire_templates/042_earned_income_tax_credit_eitc_client_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/042_earned_income_tax_credit_eitc_client_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'ak'}</t>
+          <t>ak</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'AK'}</t>
+          <t>AK</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'al'}</t>
+          <t>al</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'AL'}</t>
+          <t>AL</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'ar'}</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'AR'}</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'ca'}</t>
+          <t>ca</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'CA'}</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'co'}</t>
+          <t>co</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'CO'}</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'ct'}</t>
+          <t>ct</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'CT'}</t>
+          <t>CT</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'de'}</t>
+          <t>de</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'DE'}</t>
+          <t>DE</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'fl'}</t>
+          <t>fl</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'FL'}</t>
+          <t>FL</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'ga'}</t>
+          <t>ga</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'GA'}</t>
+          <t>GA</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'hi'}</t>
+          <t>hi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'HI'}</t>
+          <t>HI</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'ia'}</t>
+          <t>ia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'IA'}</t>
+          <t>IA</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'id'}</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'ID'}</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'il'}</t>
+          <t>il</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'IL'}</t>
+          <t>IL</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'in'}</t>
+          <t>in</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'IN'}</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'ks'}</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'KS'}</t>
+          <t>KS</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'ky'}</t>
+          <t>ky</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'KY'}</t>
+          <t>KY</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'la'}</t>
+          <t>la</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'LA'}</t>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'ma'}</t>
+          <t>ma</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'MA'}</t>
+          <t>MA</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'md'}</t>
+          <t>md</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'MD'}</t>
+          <t>MD</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'me'}</t>
+          <t>me</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'ME'}</t>
+          <t>ME</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'mi'}</t>
+          <t>mi</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'MI'}</t>
+          <t>MI</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'mn'}</t>
+          <t>mn</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'MN'}</t>
+          <t>MN</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'mo'}</t>
+          <t>mo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'MO'}</t>
+          <t>MO</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'ms'}</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'MS'}</t>
+          <t>MS</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'mt'}</t>
+          <t>mt</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'MT'}</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'nc'}</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'NC'}</t>
+          <t>NC</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'nd'}</t>
+          <t>nd</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'ND'}</t>
+          <t>ND</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'ne'}</t>
+          <t>ne</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'NE'}</t>
+          <t>NE</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'nh'}</t>
+          <t>nh</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'NH'}</t>
+          <t>NH</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'nj'}</t>
+          <t>nj</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'NJ'}</t>
+          <t>NJ</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'nm'}</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'NM'}</t>
+          <t>NM</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'nv'}</t>
+          <t>nv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'NV'}</t>
+          <t>NV</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'ny'}</t>
+          <t>ny</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'NY'}</t>
+          <t>NY</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'oh'}</t>
+          <t>oh</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'OH'}</t>
+          <t>OH</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'ok'}</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'OK'}</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'or'}</t>
+          <t>or</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'OR'}</t>
+          <t>OR</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'pa'}</t>
+          <t>pa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'PA'}</t>
+          <t>PA</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'ri'}</t>
+          <t>ri</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'RI'}</t>
+          <t>RI</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'sc'}</t>
+          <t>sc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'SC'}</t>
+          <t>SC</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'sd'}</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'SD'}</t>
+          <t>SD</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'tn'}</t>
+          <t>tn</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'TN'}</t>
+          <t>TN</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'tx'}</t>
+          <t>tx</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'TX'}</t>
+          <t>TX</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'ut'}</t>
+          <t>ut</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'UT'}</t>
+          <t>UT</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'va'}</t>
+          <t>va</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'VA'}</t>
+          <t>VA</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'wa'}</t>
+          <t>wa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'WA'}</t>
+          <t>WA</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'wi'}</t>
+          <t>wi</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'WI'}</t>
+          <t>WI</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'wv'}</t>
+          <t>wv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'WV'}</t>
+          <t>WV</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'wy'}</t>
+          <t>wy</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'WY'}</t>
+          <t>WY</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'january'}</t>
+          <t>january</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'January'}</t>
+          <t>January</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'february'}</t>
+          <t>february</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'February'}</t>
+          <t>February</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_'march'}</t>
+          <t>march</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 'March'}</t>
+          <t>March</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'april'}</t>
+          <t>april</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 'April'}</t>
+          <t>April</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_'may'}</t>
+          <t>may</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 'May'}</t>
+          <t>May</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'june'}</t>
+          <t>june</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'June'}</t>
+          <t>June</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'label':_'july'}</t>
+          <t>july</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'label': 'July'}</t>
+          <t>July</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'label':_'august'}</t>
+          <t>august</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'label': 'August'}</t>
+          <t>August</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'label':_'september'}</t>
+          <t>september</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'label': 'September'}</t>
+          <t>September</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'label':_'october'}</t>
+          <t>october</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'label': 'October'}</t>
+          <t>October</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'label':_'november'}</t>
+          <t>november</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'label': 'November'}</t>
+          <t>November</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'label':_'december'}</t>
+          <t>december</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'label': 'December'}</t>
+          <t>December</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'label':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'label': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'label':_'january'}</t>
+          <t>january</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'label': 'January'}</t>
+          <t>January</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'label':_'february'}</t>
+          <t>february</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'label': 'February'}</t>
+          <t>February</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'label':_'march'}</t>
+          <t>march</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'label': 'March'}</t>
+          <t>March</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'label':_'april'}</t>
+          <t>april</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'label': 'April'}</t>
+          <t>April</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'label':_'may'}</t>
+          <t>may</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'label': 'May'}</t>
+          <t>May</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'label':_'june'}</t>
+          <t>june</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'label': 'June'}</t>
+          <t>June</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'label':_'july'}</t>
+          <t>july</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'label': 'July'}</t>
+          <t>July</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'label':_'august'}</t>
+          <t>august</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'label': 'August'}</t>
+          <t>August</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'label':_'september'}</t>
+          <t>september</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'label': 'September'}</t>
+          <t>September</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'label':_'october'}</t>
+          <t>october</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'label': 'October'}</t>
+          <t>October</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'label':_'november'}</t>
+          <t>november</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'label': 'November'}</t>
+          <t>November</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'label':_'december'}</t>
+          <t>december</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'label': 'December'}</t>
+          <t>December</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'label':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'label': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
